--- a/EXCEL/Data/Alder_data/Alder_overenskomst.xlsx
+++ b/EXCEL/Data/Alder_data/Alder_overenskomst.xlsx
@@ -70,7 +70,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.49.34</t>
+    <t>Kørsel 14.4.2026 12.23.21</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
